--- a/2040.xlsx
+++ b/2040.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="54">
   <si>
     <t xml:space="preserve">Power Generation</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t xml:space="preserve">Ccn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fosil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fosiln</t>
   </si>
   <si>
     <t xml:space="preserve">Solarn</t>
@@ -367,10 +373,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z24"/>
-  <sheetFormatPr defaultColWidth="10.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="10.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="7" style="0" width="12.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="0" width="10.85"/>
@@ -1984,8 +1990,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B3:M27"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B3:O56"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="0" t="s">
@@ -2010,19 +2016,25 @@
         <v>48</v>
       </c>
       <c r="I3" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" s="0" t="s">
+      <c r="L3" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" s="0" t="s">
-        <v>51</v>
+      <c r="N3" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O3" s="0" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2048,10 +2060,12 @@
         <v>0</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0</v>
+        <f aca="false">C4+G4</f>
+        <v>5.82076609134674E-014</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D4+E4+H4</f>
+        <v>-2.36468622460961E-014</v>
       </c>
       <c r="K4" s="0" t="n">
         <v>0</v>
@@ -2060,6 +2074,12 @@
         <v>0</v>
       </c>
       <c r="M4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2086,9 +2106,11 @@
         <v>0</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0</v>
+        <f aca="false">C5+G5</f>
+        <v>1.94631866179406E-013</v>
       </c>
       <c r="J5" s="0" t="n">
+        <f aca="false">D5+E5+H5</f>
         <v>0</v>
       </c>
       <c r="K5" s="0" t="n">
@@ -2098,6 +2120,12 @@
         <v>0</v>
       </c>
       <c r="M5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2124,10 +2152,12 @@
         <v>-0.00195478272007313</v>
       </c>
       <c r="I6" s="0" t="n">
+        <f aca="false">C6+G6</f>
         <v>0</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D6+E6+H6</f>
+        <v>-0.0162279931598932</v>
       </c>
       <c r="K6" s="0" t="n">
         <v>0</v>
@@ -2136,6 +2166,12 @@
         <v>0</v>
       </c>
       <c r="M6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2162,10 +2198,12 @@
         <v>-37.2119633670006</v>
       </c>
       <c r="I7" s="0" t="n">
+        <f aca="false">C7+G7</f>
         <v>0</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D7+E7+H7</f>
+        <v>-61.1146222402311</v>
       </c>
       <c r="K7" s="0" t="n">
         <v>0</v>
@@ -2174,6 +2212,12 @@
         <v>0</v>
       </c>
       <c r="M7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2200,10 +2244,12 @@
         <v>-111.821390233223</v>
       </c>
       <c r="I8" s="0" t="n">
+        <f aca="false">C8+G8</f>
         <v>0</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D8+E8+H8</f>
+        <v>-194.115919482351</v>
       </c>
       <c r="K8" s="0" t="n">
         <v>0</v>
@@ -2212,6 +2258,12 @@
         <v>0</v>
       </c>
       <c r="M8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="0" t="n">
         <v>-93.8844104216735</v>
       </c>
     </row>
@@ -2238,18 +2290,26 @@
         <v>-182.469615561831</v>
       </c>
       <c r="I9" s="0" t="n">
+        <f aca="false">C9+G9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <f aca="false">D9+E9+H9</f>
+        <v>-233.315863286367</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>20.451713151906</v>
       </c>
-      <c r="J9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="0" t="n">
         <v>-9.32272515</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="O9" s="0" t="n">
         <v>-248.308751733333</v>
       </c>
     </row>
@@ -2276,18 +2336,26 @@
         <v>-226.37631532979</v>
       </c>
       <c r="I10" s="0" t="n">
+        <f aca="false">C10+G10</f>
         <v>0</v>
       </c>
       <c r="J10" s="0" t="n">
+        <f aca="false">D10+E10+H10</f>
+        <v>-251.980101155329</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="0" t="n">
         <v>-166.936</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="M10" s="0" t="n">
         <v>11.3974902</v>
       </c>
-      <c r="L10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="0" t="n">
+      <c r="N10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="0" t="n">
         <v>-85.0442777337699</v>
       </c>
     </row>
@@ -2314,18 +2382,26 @@
         <v>-183.94314363056</v>
       </c>
       <c r="I11" s="0" t="n">
+        <f aca="false">C11+G11</f>
         <v>0</v>
       </c>
       <c r="J11" s="0" t="n">
+        <f aca="false">D11+E11+H11</f>
+        <v>-201.061845461213</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="0" t="n">
         <v>-58.41</v>
       </c>
-      <c r="K11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="0" t="n">
+      <c r="M11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="0" t="n">
         <v>-13.0005522</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="O11" s="0" t="n">
         <v>-101.737338100263</v>
       </c>
     </row>
@@ -2352,10 +2428,12 @@
         <v>-86.8477773346679</v>
       </c>
       <c r="I12" s="0" t="n">
+        <f aca="false">C12+G12</f>
         <v>0</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D12+E12+H12</f>
+        <v>-119.740973833266</v>
       </c>
       <c r="K12" s="0" t="n">
         <v>0</v>
@@ -2364,6 +2442,12 @@
         <v>0</v>
       </c>
       <c r="M12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2390,10 +2474,12 @@
         <v>-0.0955298093017736</v>
       </c>
       <c r="I13" s="0" t="n">
+        <f aca="false">C13+G13</f>
         <v>0</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D13+E13+H13</f>
+        <v>-0.156892237869579</v>
       </c>
       <c r="K13" s="0" t="n">
         <v>0</v>
@@ -2402,6 +2488,12 @@
         <v>0</v>
       </c>
       <c r="M13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2428,10 +2520,12 @@
         <v>-0.0131615335114693</v>
       </c>
       <c r="I14" s="0" t="n">
+        <f aca="false">C14+G14</f>
         <v>0</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D14+E14+H14</f>
+        <v>-0.0216156868891776</v>
       </c>
       <c r="K14" s="0" t="n">
         <v>0</v>
@@ -2440,6 +2534,12 @@
         <v>0</v>
       </c>
       <c r="M14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2466,10 +2566,12 @@
         <v>0</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0</v>
+        <f aca="false">C15+G15</f>
+        <v>2.91038304567337E-013</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D15+E15+H15</f>
+        <v>-3.63797880709171E-013</v>
       </c>
       <c r="K15" s="0" t="n">
         <v>0</v>
@@ -2478,6 +2580,12 @@
         <v>0</v>
       </c>
       <c r="M15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2504,10 +2612,12 @@
         <v>0</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>0</v>
+        <f aca="false">C16+G16</f>
+        <v>3.63797880709171E-013</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D16+E16+H16</f>
+        <v>-1.81898940354586E-013</v>
       </c>
       <c r="K16" s="0" t="n">
         <v>0</v>
@@ -2516,6 +2626,12 @@
         <v>0</v>
       </c>
       <c r="M16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2542,10 +2658,12 @@
         <v>0</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>0</v>
+        <f aca="false">C17+G17</f>
+        <v>1.89174897968769E-013</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D17+E17+H17</f>
+        <v>-1.30967237055302E-013</v>
       </c>
       <c r="K17" s="0" t="n">
         <v>0</v>
@@ -2554,6 +2672,12 @@
         <v>0</v>
       </c>
       <c r="M17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2580,10 +2704,12 @@
         <v>-0.123872537258852</v>
       </c>
       <c r="I18" s="0" t="n">
+        <f aca="false">C18+G18</f>
         <v>0</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D18+E18+H18</f>
+        <v>-0.203440577586938</v>
       </c>
       <c r="K18" s="0" t="n">
         <v>0</v>
@@ -2592,6 +2718,12 @@
         <v>0</v>
       </c>
       <c r="M18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2618,10 +2750,12 @@
         <v>-46.906667545859</v>
       </c>
       <c r="I19" s="0" t="n">
+        <f aca="false">C19+G19</f>
         <v>0</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D19+E19+H19</f>
+        <v>-77.1027775632527</v>
       </c>
       <c r="K19" s="0" t="n">
         <v>0</v>
@@ -2630,6 +2764,12 @@
         <v>0</v>
       </c>
       <c r="M19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2656,18 +2796,26 @@
         <v>-84.3943223067665</v>
       </c>
       <c r="I20" s="0" t="n">
+        <f aca="false">C20+G20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <f aca="false">D20+E20+H20</f>
+        <v>-159.436848110342</v>
+      </c>
+      <c r="K20" s="0" t="n">
         <v>8.49905904544329</v>
       </c>
-      <c r="J20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="0" t="n">
+      <c r="L20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="0" t="n">
         <v>7.4682648</v>
       </c>
-      <c r="L20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="0" t="n">
+      <c r="N20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="0" t="n">
         <v>-182.609694624793</v>
       </c>
     </row>
@@ -2694,10 +2842,12 @@
         <v>-183.014959685773</v>
       </c>
       <c r="I21" s="0" t="n">
+        <f aca="false">C21+G21</f>
         <v>0</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D21+E21+H21</f>
+        <v>-228.752005272908</v>
       </c>
       <c r="K21" s="0" t="n">
         <v>0</v>
@@ -2706,6 +2856,12 @@
         <v>0</v>
       </c>
       <c r="M21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="0" t="n">
         <v>-232.822333609954</v>
       </c>
     </row>
@@ -2732,18 +2888,26 @@
         <v>-216.688049009412</v>
       </c>
       <c r="I22" s="0" t="n">
+        <f aca="false">C22+G22</f>
         <v>0</v>
       </c>
       <c r="J22" s="0" t="n">
+        <f aca="false">D22+E22+H22</f>
+        <v>-233.068181094412</v>
+      </c>
+      <c r="K22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="0" t="n">
         <v>-70.3</v>
       </c>
-      <c r="K22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="0" t="n">
         <v>-156.266911011383</v>
       </c>
     </row>
@@ -2770,18 +2934,26 @@
         <v>-172.271293845623</v>
       </c>
       <c r="I23" s="0" t="n">
+        <f aca="false">C23+G23</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <f aca="false">D23+E23+H23</f>
+        <v>-186.59666881965</v>
+      </c>
+      <c r="K23" s="0" t="n">
         <v>38.9723302513592</v>
       </c>
-      <c r="J23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="0" t="n">
         <v>-12.9350691</v>
       </c>
-      <c r="M23" s="0" t="n">
+      <c r="O23" s="0" t="n">
         <v>-204.19397480977</v>
       </c>
     </row>
@@ -2808,18 +2980,26 @@
         <v>-29.5936847737346</v>
       </c>
       <c r="I24" s="0" t="n">
+        <f aca="false">C24+G24</f>
         <v>0</v>
       </c>
       <c r="J24" s="0" t="n">
+        <f aca="false">D24+E24+H24</f>
+        <v>-58.1253746915271</v>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="0" t="n">
         <v>-12.1414280752992</v>
       </c>
-      <c r="K24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="0" t="n">
         <v>-57.7718892093573</v>
       </c>
     </row>
@@ -2846,18 +3026,26 @@
         <v>-0.486199951659248</v>
       </c>
       <c r="I25" s="0" t="n">
+        <f aca="false">C25+G25</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="0" t="n">
+        <f aca="false">D25+E25+H25</f>
+        <v>-2.06483709818412</v>
+      </c>
+      <c r="K25" s="0" t="n">
         <v>1.342</v>
       </c>
-      <c r="J25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="0" t="n">
+      <c r="L25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="0" t="n">
         <v>12.081843</v>
       </c>
-      <c r="L25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="0" t="n">
+      <c r="N25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="0" t="n">
         <v>-15.3952854377422</v>
       </c>
     </row>
@@ -2884,18 +3072,26 @@
         <v>0</v>
       </c>
       <c r="I26" s="0" t="n">
-        <v>0</v>
+        <f aca="false">C26+G26</f>
+        <v>5.82076609134674E-014</v>
       </c>
       <c r="J26" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D26+E26+H26</f>
+        <v>-5.82076609134674E-014</v>
       </c>
       <c r="K26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="0" t="n">
         <v>10.8095706</v>
       </c>
-      <c r="L26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="0" t="n">
+      <c r="N26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="0" t="n">
         <v>-10.8095705999999</v>
       </c>
     </row>
@@ -2922,10 +3118,12 @@
         <v>0</v>
       </c>
       <c r="I27" s="0" t="n">
-        <v>0</v>
+        <f aca="false">C27+G27</f>
+        <v>2.5465851649642E-014</v>
       </c>
       <c r="J27" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D27+E27+H27</f>
+        <v>-1.45519152283669E-013</v>
       </c>
       <c r="K27" s="0" t="n">
         <v>0</v>
@@ -2934,6 +3132,662 @@
         <v>0</v>
       </c>
       <c r="M27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F32" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="G32" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H32" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="I32" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="J32" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="K32" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="L32" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="M32" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F33" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>5.82076609134674E-014</v>
+      </c>
+      <c r="H33" s="0" t="n">
+        <v>-2.36468622460961E-014</v>
+      </c>
+      <c r="I33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F34" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>1.94631866179406E-013</v>
+      </c>
+      <c r="H34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F35" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="0" t="n">
+        <v>-0.0162279931598932</v>
+      </c>
+      <c r="I35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F36" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="G36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="0" t="n">
+        <v>-61.1146222402311</v>
+      </c>
+      <c r="I36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F37" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="G37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="0" t="n">
+        <v>-194.115919482351</v>
+      </c>
+      <c r="I37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="0" t="n">
+        <v>-93.8844104216735</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F38" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="0" t="n">
+        <v>-233.315863286367</v>
+      </c>
+      <c r="I38" s="0" t="n">
+        <v>20.451713151906</v>
+      </c>
+      <c r="J38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="0" t="n">
+        <v>-9.32272515</v>
+      </c>
+      <c r="M38" s="0" t="n">
+        <v>-248.308751733333</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F39" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="0" t="n">
+        <v>-251.980101155329</v>
+      </c>
+      <c r="I39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="0" t="n">
+        <v>-166.936</v>
+      </c>
+      <c r="K39" s="0" t="n">
+        <v>11.3974902</v>
+      </c>
+      <c r="L39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="0" t="n">
+        <v>-85.0442777337699</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F40" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="0" t="n">
+        <v>-201.061845461213</v>
+      </c>
+      <c r="I40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="0" t="n">
+        <v>-58.41</v>
+      </c>
+      <c r="K40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="0" t="n">
+        <v>-13.0005522</v>
+      </c>
+      <c r="M40" s="0" t="n">
+        <v>-101.737338100263</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F41" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="0" t="n">
+        <v>-119.740973833266</v>
+      </c>
+      <c r="I41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F42" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="0" t="n">
+        <v>-0.156892237869579</v>
+      </c>
+      <c r="I42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F43" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="0" t="n">
+        <v>-0.0216156868891776</v>
+      </c>
+      <c r="I43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F44" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="0" t="n">
+        <v>2.91038304567337E-013</v>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>-3.63797880709171E-013</v>
+      </c>
+      <c r="I44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F45" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="G45" s="0" t="n">
+        <v>3.63797880709171E-013</v>
+      </c>
+      <c r="H45" s="0" t="n">
+        <v>-1.81898940354586E-013</v>
+      </c>
+      <c r="I45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F46" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" s="0" t="n">
+        <v>1.89174897968769E-013</v>
+      </c>
+      <c r="H46" s="0" t="n">
+        <v>-1.30967237055302E-013</v>
+      </c>
+      <c r="I46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F47" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="0" t="n">
+        <v>-0.203440577586938</v>
+      </c>
+      <c r="I47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F48" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="0" t="n">
+        <v>-77.1027775632527</v>
+      </c>
+      <c r="I48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F49" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="0" t="n">
+        <v>-159.436848110342</v>
+      </c>
+      <c r="I49" s="0" t="n">
+        <v>8.49905904544329</v>
+      </c>
+      <c r="J49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="0" t="n">
+        <v>7.4682648</v>
+      </c>
+      <c r="L49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="0" t="n">
+        <v>-182.609694624793</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F50" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="0" t="n">
+        <v>-228.752005272908</v>
+      </c>
+      <c r="I50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="0" t="n">
+        <v>-232.822333609954</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F51" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="0" t="n">
+        <v>-233.068181094412</v>
+      </c>
+      <c r="I51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="0" t="n">
+        <v>-70.3</v>
+      </c>
+      <c r="K51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="0" t="n">
+        <v>-156.266911011383</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F52" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="0" t="n">
+        <v>-186.59666881965</v>
+      </c>
+      <c r="I52" s="0" t="n">
+        <v>38.9723302513592</v>
+      </c>
+      <c r="J52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="0" t="n">
+        <v>-12.9350691</v>
+      </c>
+      <c r="M52" s="0" t="n">
+        <v>-204.19397480977</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F53" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="0" t="n">
+        <v>-58.1253746915271</v>
+      </c>
+      <c r="I53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="0" t="n">
+        <v>-12.1414280752992</v>
+      </c>
+      <c r="K53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="0" t="n">
+        <v>-57.7718892093573</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F54" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>-2.06483709818412</v>
+      </c>
+      <c r="I54" s="0" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="J54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="0" t="n">
+        <v>12.081843</v>
+      </c>
+      <c r="L54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="0" t="n">
+        <v>-15.3952854377422</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F55" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="G55" s="0" t="n">
+        <v>5.82076609134674E-014</v>
+      </c>
+      <c r="H55" s="0" t="n">
+        <v>-5.82076609134674E-014</v>
+      </c>
+      <c r="I55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="0" t="n">
+        <v>10.8095706</v>
+      </c>
+      <c r="L55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="0" t="n">
+        <v>-10.8095705999999</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F56" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" s="0" t="n">
+        <v>2.5465851649642E-014</v>
+      </c>
+      <c r="H56" s="0" t="n">
+        <v>-1.45519152283669E-013</v>
+      </c>
+      <c r="I56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="0" t="n">
         <v>0</v>
       </c>
     </row>
